--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MARYLAND_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MARYLAND_2010.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C76">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C270">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C309">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C525">
